--- a/output/pdf_financials_xlsx/SIS.xlsx
+++ b/output/pdf_financials_xlsx/SIS.xlsx
@@ -1068,16 +1068,16 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.426</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.873</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.492</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.497</v>
       </c>
     </row>
     <row r="13">
@@ -2030,16 +2030,16 @@
         <v>20.128</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>47.472</v>
+        <v>47.898</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>50.315</v>
+        <v>51.188</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>65.66500000000001</v>
+        <v>66.157</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>90.26300000000001</v>
+        <v>90.76000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2146,16 +2146,16 @@
         <v>53.195</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>77.95399999999999</v>
+        <v>78.38</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>80.925</v>
+        <v>81.798</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>96.79600000000001</v>
+        <v>97.288</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>120.711</v>
+        <v>121.208</v>
       </c>
     </row>
     <row r="30">
@@ -2208,16 +2208,16 @@
         <v>8.04786204788928</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>9.878961995511292</v>
+        <v>9.932948164406893</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>9.668990171502854</v>
+        <v>9.773296979284405</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>11.15467144216963</v>
+        <v>11.21136901592833</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>13.21373095704889</v>
+        <v>13.26813547930165</v>
       </c>
     </row>
     <row r="31">
@@ -2360,34 +2360,34 @@
         <v>4.823164</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>6.04062</v>
+        <v>0.823</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.931</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.993</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.968</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>16.28</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>29.707</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>51.23</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>7.719</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>11.43</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>39.696</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>63.494</v>
@@ -2476,34 +2476,34 @@
         <v>4.823164</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>6.04062</v>
+        <v>0.823</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.931</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.993</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.968</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>16.28</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>29.707</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>51.23</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>7.719</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>11.43</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>39.696</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>63.494</v>
@@ -3175,31 +3175,31 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>6.611</v>
+        <v>2.68</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.01</v>
+        <v>1.042</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>17.278</v>
+        <v>0.998</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>30.568</v>
+        <v>0.861</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>52.287</v>
+        <v>1.057</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>11.339</v>
+        <v>3.62</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>16.007</v>
+        <v>4.577</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>45.9</v>
+        <v>6.204</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>26.239</v>
@@ -7626,7 +7626,7 @@
         <v>-16.394</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>-5.364</v>
+        <v>-7.677</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>-113.709</v>
@@ -7684,7 +7684,7 @@
         <v>-16.394</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-5.364</v>
+        <v>-7.677</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>-113.709</v>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -20328,7 +20328,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -24098,7 +24098,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -27431,7 +27431,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -28962,7 +28962,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -48400,7 +48400,11 @@
           <t>Lease payments 12</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -72633,7 +72637,7 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">

--- a/output/pdf_financials_xlsx/SIS.xlsx
+++ b/output/pdf_financials_xlsx/SIS.xlsx
@@ -1096,13 +1096,13 @@
         <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>0.517</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>0.781</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>0.29</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>-0</v>
@@ -1117,25 +1117,25 @@
         <v>-0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.979</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-6.526</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-15.756</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>-16.469</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>-21.835</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0</v>
+        <v>-18.472</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-0</v>
+        <v>-15.117</v>
       </c>
     </row>
     <row r="14">
@@ -2000,13 +2000,13 @@
         <v>0.408</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.645</v>
+        <v>2.128</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.033</v>
+        <v>-0.748</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>6.598</v>
+        <v>6.308</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>8.015000000000001</v>
@@ -2021,25 +2021,25 @@
         <v>19.248</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>24.6</v>
+        <v>26.579</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>30.687</v>
+        <v>37.213</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>20.128</v>
+        <v>35.884</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>47.898</v>
+        <v>64.367</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>51.188</v>
+        <v>73.023</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>66.157</v>
+        <v>84.629</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>90.76000000000001</v>
+        <v>105.877</v>
       </c>
     </row>
     <row r="28">
@@ -2055,7 +2055,7 @@
         <v>0.438885</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.819</v>
+        <v>0.775013</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0.792</v>
@@ -2082,22 +2082,22 @@
         <v>6.153</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>6.906</v>
+        <v>9.895</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>33.067</v>
+        <v>42.485</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>30.482</v>
+        <v>41.049</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>30.61</v>
+        <v>40.671</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>31.131</v>
+        <v>42.821</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>30.448</v>
+        <v>43.691</v>
       </c>
     </row>
     <row r="29">
@@ -2113,16 +2113,16 @@
         <v>3.340538</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.227</v>
+        <v>1.183013</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.437</v>
+        <v>2.92</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.785</v>
+        <v>0.004</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7.363</v>
+        <v>7.073</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>8.802</v>
@@ -2137,25 +2137,25 @@
         <v>23.219</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>30.753</v>
+        <v>32.732</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>37.593</v>
+        <v>47.108</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>53.195</v>
+        <v>78.369</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>78.38</v>
+        <v>105.416</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>81.798</v>
+        <v>113.694</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>97.288</v>
+        <v>127.45</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>121.208</v>
+        <v>149.568</v>
       </c>
     </row>
     <row r="30">
@@ -2171,16 +2171,16 @@
         <v>6.054734979081179</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>519.9152542372882</v>
+        <v>501.2766949152542</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5.265496215951221</v>
+        <v>4.473450378404878</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>106.9482288828338</v>
+        <v>0.544959128065395</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>9.721543722520762</v>
+        <v>9.338649836940018</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>10.61645900927523</v>
@@ -2199,25 +2199,25 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>10.75151905018284</v>
+        <v>11.44339484117273</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>10.0424747555698</v>
+        <v>12.5842816690709</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>8.04786204788928</v>
+        <v>11.85643201111072</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>9.932948164406893</v>
+        <v>13.35916896783768</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>9.773296979284405</v>
+        <v>13.58425911101447</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>11.21136901592833</v>
+        <v>14.68720686086738</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>13.26813547930165</v>
+        <v>16.37258668873498</v>
       </c>
     </row>
     <row r="31">
@@ -6185,55 +6185,55 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.409857</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.438885</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.819</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.792</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.752</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.765</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.787</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.747</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>3.971</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>6.153</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>9.895</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>42.485</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>41.049</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>40.671</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>42.821</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>43.691</v>
       </c>
     </row>
     <row r="101">
@@ -39915,7 +39915,11 @@
           <t>Depreciation of right-of-use assets 13</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -40010,7 +40014,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -46519,7 +46523,11 @@
           <t>Depreciation of right-of-use assets 12</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -46622,7 +46630,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -58878,7 +58886,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -65868,7 +65876,7 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E583" s="5" t="n">
@@ -71499,7 +71507,11 @@
           <t>Net finance costs 22</t>
         </is>
       </c>
-      <c r="D640" t="inlineStr"/>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E640" t="inlineStr">
         <is>
           <t>-</t>
@@ -73823,7 +73835,11 @@
           <t>Net finance costs 21</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E664" t="inlineStr">
         <is>
           <t>-</t>
@@ -74322,7 +74338,11 @@
           <t>Net Finance costs 18</t>
         </is>
       </c>
-      <c r="D669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E669" t="inlineStr">
         <is>
           <t>-</t>
@@ -80943,7 +80963,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D736" t="inlineStr"/>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E736" t="inlineStr">
         <is>
           <t>-</t>
@@ -85056,7 +85080,7 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E777" s="5" t="n">

--- a/output/pdf_financials_xlsx/SIS.xlsx
+++ b/output/pdf_financials_xlsx/SIS.xlsx
@@ -2711,46 +2711,46 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>4.176</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>1.385</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>1.752</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>2.424</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>5.444</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>4.816</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>3.394</v>
       </c>
     </row>
     <row r="41">
@@ -2769,46 +2769,46 @@
         <v>0.455</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>9.119999999999999</v>
+        <v>9.237</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.592</v>
+        <v>0.861</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>11.711</v>
+        <v>11.848</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>12.168</v>
+        <v>12.347</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>12.878</v>
+        <v>13</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>13.16</v>
+        <v>13.207</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>24.483</v>
+        <v>24.798</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>50.317</v>
+        <v>54.493</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>48.268</v>
+        <v>49.653</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>102.497</v>
+        <v>104.249</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99.45</v>
+        <v>101.874</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>114.701</v>
+        <v>120.145</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>112.441</v>
+        <v>117.257</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>115.533</v>
+        <v>118.927</v>
       </c>
     </row>
     <row r="42">
@@ -3175,46 +3175,46 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.68</v>
+        <v>2.563</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.042</v>
+        <v>0.905</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.998</v>
+        <v>0.819</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.861</v>
+        <v>0.739</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.057</v>
+        <v>1.01</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>3.62</v>
+        <v>3.305</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.577</v>
+        <v>0.401</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>6.204</v>
+        <v>4.819</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>26.239</v>
+        <v>24.487</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>38.878</v>
+        <v>36.454</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>25.072</v>
+        <v>19.628</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>31.835</v>
+        <v>27.019</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>18.156</v>
+        <v>14.762</v>
       </c>
     </row>
     <row r="49">
@@ -3923,10 +3923,10 @@
         <v>9.156000000000001</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0</v>
+        <v>60.553</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0</v>
+        <v>110.867</v>
       </c>
       <c r="M60" s="3" t="n">
         <v>0</v>
@@ -6685,7 +6685,7 @@
         <v>0</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>0</v>
+        <v>2.288</v>
       </c>
       <c r="O108" s="3" t="n">
         <v>0</v>
@@ -7058,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.035721</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>4.209682</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7425,16 +7425,16 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.346</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.418</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-0.076</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -7535,37 +7535,37 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0</v>
+        <v>7.700095</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0</v>
+        <v>2.628</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>0.664</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0</v>
+        <v>2.649</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0</v>
+        <v>39.495</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M123" s="3" t="n">
         <v>0</v>
@@ -7651,37 +7651,37 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>-0.518006</v>
+        <v>5.481994</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>-5.543619</v>
+        <v>2.156476</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>-2.182731</v>
+        <v>-2.141731</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>2.628</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>0.664</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-2.696</v>
+        <v>-0.047</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-16.356</v>
+        <v>23.139</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-16.394</v>
+        <v>33.606</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>-7.677</v>
@@ -14151,7 +14151,11 @@
           <t>Intangible assets and goodwill 8</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -44632,7 +44636,11 @@
           <t>Impairment loss on goodwill 9</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -48210,7 +48218,11 @@
           <t>Increase in long-term debt 11</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -54465,7 +54477,11 @@
           <t>Increase in long-term debt 13</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>
@@ -57621,7 +57637,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
           <t>-</t>
@@ -58106,7 +58126,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -60781,7 +60805,11 @@
           <t>Increase in long-term debt 564</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -61181,7 +61209,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr">
         <is>
           <t>-</t>
@@ -64882,7 +64914,11 @@
           <t>Increase in long-term debt 2 628</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E573" t="inlineStr">
         <is>
           <t>-</t>
@@ -66173,7 +66209,11 @@
           <t>Future income taxes (note 17B)</t>
         </is>
       </c>
-      <c r="D586" t="inlineStr"/>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E586" t="inlineStr">
         <is>
           <t>-</t>
@@ -67072,7 +67112,11 @@
           <t>Proceeds from long-term investments</t>
         </is>
       </c>
-      <c r="D595" t="inlineStr"/>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E595" t="inlineStr">
         <is>
           <t>-</t>
@@ -67959,7 +68003,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E604" s="5" t="n">
         <v>6</v>
       </c>
@@ -69052,7 +69100,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E615" s="5" t="n">
         <v>1.548132</v>
       </c>
